--- a/10_Каталог_неисправностей/Каталог_неисправностей.xlsx
+++ b/10_Каталог_неисправностей/Каталог_неисправностей.xlsx
@@ -64,7 +64,7 @@
     <t xml:space="preserve">СТД-001, РГЛ-001, ЭНЦ-001, RAG-0002</t>
   </si>
   <si>
-    <t xml:space="preserve">Промывка теплообменных пластин/трубок (РГЛ-001, раздел 2) — 12_Типовые_решения пока не наполнен</t>
+    <t xml:space="preserve">РЕШ-001 — Промывка теплообменных пластин/трубок (12_Типовые_решения)</t>
   </si>
   <si>
     <t xml:space="preserve">НСП-002</t>
@@ -85,7 +85,7 @@
     <t xml:space="preserve">СТД-002, ЭНЦ-002, RAG-0004</t>
   </si>
   <si>
-    <t xml:space="preserve">Механическая или химическая очистка поверхностей нагрева — 12_Типовые_решения пока не наполнен</t>
+    <t xml:space="preserve">РЕШ-002 — Очистка поверхностей нагрева котла (12_Типовые_решения)</t>
   </si>
   <si>
     <t xml:space="preserve">НСП-003</t>
@@ -103,7 +103,7 @@
     <t xml:space="preserve">СТД-002, ЭНЦ-002</t>
   </si>
   <si>
-    <t xml:space="preserve">Наладка режима горения — 12_Типовые_решения пока не наполнен</t>
+    <t xml:space="preserve">РЕШ-003 — Наладка режима горения (12_Типовые_решения)</t>
   </si>
   <si>
     <t xml:space="preserve">НСП-004</t>
@@ -124,7 +124,7 @@
     <t xml:space="preserve">СТД-003, ЭНЦ-003</t>
   </si>
   <si>
-    <t xml:space="preserve">Замена рабочего колеса — 12_Типовые_решения пока не наполнен</t>
+    <t xml:space="preserve">РЕШ-004 — Замена рабочего колеса насоса (12_Типовые_решения)</t>
   </si>
   <si>
     <t xml:space="preserve">НСП-005</t>
@@ -139,7 +139,7 @@
     <t xml:space="preserve">Образование и схлопывание пузырьков пара в зоне пониженного давления на входе в рабочее колесо (см. ЭНЦ-003)</t>
   </si>
   <si>
-    <t xml:space="preserve">Проверка условий на всасывании (подпор, гидравлическое сопротивление всасывающего трубопровода) — 12_Типовые_решения пока не наполнен</t>
+    <t xml:space="preserve">РЕШ-005 — Устранение условий кавитации (12_Типовые_решения)</t>
   </si>
   <si>
     <t xml:space="preserve">НСП-006</t>
@@ -160,7 +160,7 @@
     <t xml:space="preserve">СТД-003, RAG-0005</t>
   </si>
   <si>
-    <t xml:space="preserve">Замена подшипников — 12_Типовые_решения пока не наполнен</t>
+    <t xml:space="preserve">РЕШ-006 — Замена подшипников насоса (12_Типовые_решения)</t>
   </si>
   <si>
     <t xml:space="preserve">НСП-007</t>
@@ -175,7 +175,7 @@
     <t xml:space="preserve">Неравномерный износ рабочего колеса, ослабление крепежа ротора, засорение колеса посторонними включениями</t>
   </si>
   <si>
-    <t xml:space="preserve">Балансировка ротора — 12_Типовые_решения пока не наполнен</t>
+    <t xml:space="preserve">РЕШ-007 — Балансировка ротора насоса (12_Типовые_решения)</t>
   </si>
 </sst>
 </file>
@@ -286,8 +286,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -583,195 +587,195 @@
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="40"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+    <row r="3" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+    <row r="4" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+    <row r="5" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+    <row r="6" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+    <row r="7" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+    <row r="8" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="3" t="s">
         <v>50</v>
       </c>
     </row>

--- a/10_Каталог_неисправностей/Каталог_неисправностей.xlsx
+++ b/10_Каталог_неисправностей/Каталог_неисправностей.xlsx
@@ -82,7 +82,7 @@
     <t xml:space="preserve">Сажа и накипь на поверхностях нагрева со стороны газового тракта, ухудшающие теплопередачу (см. ЭНЦ-002)</t>
   </si>
   <si>
-    <t xml:space="preserve">СТД-002, ЭНЦ-002, RAG-0004</t>
+    <t xml:space="preserve">СТД-002, РГЛ-002, ЭНЦ-002, RAG-0004</t>
   </si>
   <si>
     <t xml:space="preserve">РЕШ-002 — Очистка поверхностей нагрева котла (12_Типовые_решения)</t>
@@ -100,7 +100,7 @@
     <t xml:space="preserve">Отклонение от оптимального соотношения топливо/воздух в горелке (см. ЭНЦ-002)</t>
   </si>
   <si>
-    <t xml:space="preserve">СТД-002, ЭНЦ-002</t>
+    <t xml:space="preserve">СТД-002, РГЛ-002, ЭНЦ-002</t>
   </si>
   <si>
     <t xml:space="preserve">РЕШ-003 — Наладка режима горения (12_Типовые_решения)</t>
@@ -121,7 +121,7 @@
     <t xml:space="preserve">Эрозионный износ рабочего колеса, в том числе как следствие длительной кавитации (см. ЭНЦ-003)</t>
   </si>
   <si>
-    <t xml:space="preserve">СТД-003, ЭНЦ-003</t>
+    <t xml:space="preserve">СТД-003, РГЛ-003, ЭНЦ-003</t>
   </si>
   <si>
     <t xml:space="preserve">РЕШ-004 — Замена рабочего колеса насоса (12_Типовые_решения)</t>
@@ -157,7 +157,7 @@
     <t xml:space="preserve">Естественный износ, недостаточная смазка, работа за пределами допустимой вибрации без своевременного вмешательства</t>
   </si>
   <si>
-    <t xml:space="preserve">СТД-003, RAG-0005</t>
+    <t xml:space="preserve">СТД-003, РГЛ-003, RAG-0005</t>
   </si>
   <si>
     <t xml:space="preserve">РЕШ-006 — Замена подшипников насоса (12_Типовые_решения)</t>
@@ -291,15 +291,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>

--- a/10_Каталог_неисправностей/Каталог_неисправностей.xlsx
+++ b/10_Каталог_неисправностей/Каталог_неисправностей.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Каталог неисправностей" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Каталог неисправностей'!$A$1:$G$8</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Каталог неисправностей'!$A$1:$G$12</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="76">
   <si>
     <t xml:space="preserve">Код</t>
   </si>
@@ -176,6 +176,81 @@
   </si>
   <si>
     <t xml:space="preserve">РЕШ-007 — Балансировка ротора насоса (12_Типовые_решения)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">НСП-008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Накипеобразование на ТЭН</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Электрические котлы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Рост времени выхода на рабочую температуру при неизменной потребляемой мощности</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Отложения накипи на поверхности ТЭН создают локальное термическое сопротивление, вызывающее перегрев спирали внутри (см. ЭНЦ-004)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">СТД-004, ЭНЦ-004, РГЛ-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">РЕШ-008 — Очистка ТЭН от накипи (12_Типовые_решения)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">НСП-009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Утечка тока / повреждение изоляции ТЭН</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Срабатывание УЗО при включении котла; резкое падение сопротивления изоляции</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пробой или начинающееся повреждение изоляции нагревательного элемента (прессованный диэлектрик ТЭН)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">СТД-004, РГЛ-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">РЕШ-009 — Замена ТЭН при пробое изоляции (12_Типовые_решения)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">НСП-010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Зашлаковывание колосниковой решётки</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Твердотопливные котлы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Снижение тяги при неизменном положении шибера; неравномерное горение, частое затухание</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Спекание золы в плотный шлак, физически перекрывающий проходные отверстия для воздуха (см. ЭНЦ-005)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">СТД-005, ЭНЦ-005, РГЛ-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">РЕШ-010 — Очистка колосниковой решётки от шлака (12_Типовые_решения)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">НСП-011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Недостаточная тяга (засорение дымохода)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Задымление в котельной, неполное сгорание топлива (тёмный дым), постепенное снижение тяги по всей высоте тракта</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Засорение дымохода сажей или посторонними предметами, в отличие от НСП-010 проявляется не резко, а постепенно</t>
+  </si>
+  <si>
+    <t xml:space="preserve">РЕШ-011 — Прочистка дымохода и проверка тяги (12_Типовые_решения)</t>
   </si>
 </sst>
 </file>
@@ -584,7 +659,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
@@ -779,8 +854,100 @@
         <v>50</v>
       </c>
     </row>
+    <row r="9" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G8"/>
+  <autoFilter ref="A1:G12"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
